--- a/disc_avg_diagnostic.xlsx
+++ b/disc_avg_diagnostic.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>European</t>
+          <t>American (Longstaff-Schwartz)</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.046039</v>
+        <v>11.051618</v>
       </c>
     </row>
     <row r="5">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D2" t="n">
         <v>100</v>
@@ -563,7 +563,7 @@
         <v>0.003277</v>
       </c>
       <c r="C3" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D3" t="n">
         <v>99.99999473332564</v>
@@ -577,7 +577,7 @@
         <v>0.006553</v>
       </c>
       <c r="C4" t="n">
-        <v>10.04603916208912</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D4" t="n">
         <v>100.0003107715358</v>
@@ -591,7 +591,7 @@
         <v>0.00983</v>
       </c>
       <c r="C5" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D5" t="n">
         <v>100.0004507069517</v>
@@ -605,7 +605,7 @@
         <v>0.013107</v>
       </c>
       <c r="C6" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D6" t="n">
         <v>100.0004298414561</v>
@@ -619,7 +619,7 @@
         <v>0.016384</v>
       </c>
       <c r="C7" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D7" t="n">
         <v>100.000281900412</v>
@@ -633,7 +633,7 @@
         <v>0.01966</v>
       </c>
       <c r="C8" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D8" t="n">
         <v>100.0004478195511</v>
@@ -647,7 +647,7 @@
         <v>0.022937</v>
       </c>
       <c r="C9" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166604</v>
       </c>
       <c r="D9" t="n">
         <v>100.0011043391456</v>
@@ -661,7 +661,7 @@
         <v>0.026214</v>
       </c>
       <c r="C10" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D10" t="n">
         <v>100.0012968193511</v>
@@ -675,7 +675,7 @@
         <v>0.02949</v>
       </c>
       <c r="C11" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166615</v>
       </c>
       <c r="D11" t="n">
         <v>100.0009352575364</v>
@@ -689,7 +689,7 @@
         <v>0.032767</v>
       </c>
       <c r="C12" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D12" t="n">
         <v>100.0010866413209</v>
@@ -703,7 +703,7 @@
         <v>0.036044</v>
       </c>
       <c r="C13" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D13" t="n">
         <v>100.0011731841288</v>
@@ -717,7 +717,7 @@
         <v>0.039321</v>
       </c>
       <c r="C14" t="n">
-        <v>10.04603916208909</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D14" t="n">
         <v>100.0008001092683</v>
@@ -731,7 +731,7 @@
         <v>0.042597</v>
       </c>
       <c r="C15" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D15" t="n">
         <v>100.0015404069079</v>
@@ -745,7 +745,7 @@
         <v>0.045874</v>
       </c>
       <c r="C16" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D16" t="n">
         <v>100.0019733367907</v>
@@ -759,7 +759,7 @@
         <v>0.049151</v>
       </c>
       <c r="C17" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D17" t="n">
         <v>100.0020491354604</v>
@@ -773,7 +773,7 @@
         <v>0.052427</v>
       </c>
       <c r="C18" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D18" t="n">
         <v>100.0007653425755</v>
@@ -787,7 +787,7 @@
         <v>0.055704</v>
       </c>
       <c r="C19" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D19" t="n">
         <v>100.0021635713697</v>
@@ -801,7 +801,7 @@
         <v>0.058981</v>
       </c>
       <c r="C20" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D20" t="n">
         <v>100.0008488016709</v>
@@ -815,7 +815,7 @@
         <v>0.062258</v>
       </c>
       <c r="C21" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D21" t="n">
         <v>100.0012373871837</v>
@@ -829,7 +829,7 @@
         <v>0.065534</v>
       </c>
       <c r="C22" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D22" t="n">
         <v>99.99963089919014</v>
@@ -843,7 +843,7 @@
         <v>0.068811</v>
       </c>
       <c r="C23" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D23" t="n">
         <v>99.99950008989012</v>
@@ -857,7 +857,7 @@
         <v>0.072088</v>
       </c>
       <c r="C24" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D24" t="n">
         <v>100.0017190306504</v>
@@ -871,7 +871,7 @@
         <v>0.075364</v>
       </c>
       <c r="C25" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D25" t="n">
         <v>100.0024782715941</v>
@@ -885,7 +885,7 @@
         <v>0.078641</v>
       </c>
       <c r="C26" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D26" t="n">
         <v>100.0013519173322</v>
@@ -899,7 +899,7 @@
         <v>0.081918</v>
       </c>
       <c r="C27" t="n">
-        <v>10.04603916208912</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D27" t="n">
         <v>100.0017187364069</v>
@@ -913,7 +913,7 @@
         <v>0.08519500000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>10.04603916208914</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D28" t="n">
         <v>100.0025900547275</v>
@@ -927,7 +927,7 @@
         <v>0.08847099999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D29" t="n">
         <v>100.0037320928651</v>
@@ -941,7 +941,7 @@
         <v>0.091748</v>
       </c>
       <c r="C30" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D30" t="n">
         <v>100.0025788796087</v>
@@ -955,7 +955,7 @@
         <v>0.095025</v>
       </c>
       <c r="C31" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D31" t="n">
         <v>100.0000570068269</v>
@@ -969,7 +969,7 @@
         <v>0.098301</v>
       </c>
       <c r="C32" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D32" t="n">
         <v>100.0016350703608</v>
@@ -983,7 +983,7 @@
         <v>0.101578</v>
       </c>
       <c r="C33" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D33" t="n">
         <v>100.0016631254799</v>
@@ -997,7 +997,7 @@
         <v>0.104855</v>
       </c>
       <c r="C34" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D34" t="n">
         <v>100.0012758080596</v>
@@ -1011,7 +1011,7 @@
         <v>0.108132</v>
       </c>
       <c r="C35" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D35" t="n">
         <v>100.0003725405476</v>
@@ -1025,7 +1025,7 @@
         <v>0.111408</v>
       </c>
       <c r="C36" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D36" t="n">
         <v>100.0004531490578</v>
@@ -1039,7 +1039,7 @@
         <v>0.114685</v>
       </c>
       <c r="C37" t="n">
-        <v>10.04603916208917</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D37" t="n">
         <v>99.99773704276437</v>
@@ -1053,7 +1053,7 @@
         <v>0.117962</v>
       </c>
       <c r="C38" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D38" t="n">
         <v>99.99711356751776</v>
@@ -1067,7 +1067,7 @@
         <v>0.121238</v>
       </c>
       <c r="C39" t="n">
-        <v>10.04603916208911</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D39" t="n">
         <v>99.99832038657145</v>
@@ -1081,7 +1081,7 @@
         <v>0.124515</v>
       </c>
       <c r="C40" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D40" t="n">
         <v>99.99667411089027</v>
@@ -1095,7 +1095,7 @@
         <v>0.127792</v>
       </c>
       <c r="C41" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D41" t="n">
         <v>99.99669087186172</v>
@@ -1109,7 +1109,7 @@
         <v>0.131068</v>
       </c>
       <c r="C42" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D42" t="n">
         <v>99.99629124702271</v>
@@ -1123,7 +1123,7 @@
         <v>0.134345</v>
       </c>
       <c r="C43" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D43" t="n">
         <v>99.99644909273822</v>
@@ -1137,7 +1137,7 @@
         <v>0.137622</v>
       </c>
       <c r="C44" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D44" t="n">
         <v>99.99659046484526</v>
@@ -1151,7 +1151,7 @@
         <v>0.140899</v>
       </c>
       <c r="C45" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D45" t="n">
         <v>99.99393130509888</v>
@@ -1165,7 +1165,7 @@
         <v>0.144175</v>
       </c>
       <c r="C46" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166614</v>
       </c>
       <c r="D46" t="n">
         <v>99.99234173923537</v>
@@ -1179,7 +1179,7 @@
         <v>0.147452</v>
       </c>
       <c r="C47" t="n">
-        <v>10.0460391620891</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D47" t="n">
         <v>99.99160785446803</v>
@@ -1193,7 +1193,7 @@
         <v>0.150729</v>
       </c>
       <c r="C48" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D48" t="n">
         <v>99.9909920742941</v>
@@ -1207,7 +1207,7 @@
         <v>0.154005</v>
       </c>
       <c r="C49" t="n">
-        <v>10.04603916208915</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D49" t="n">
         <v>99.9907091598198</v>
@@ -1221,7 +1221,7 @@
         <v>0.157282</v>
       </c>
       <c r="C50" t="n">
-        <v>10.04603916208909</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D50" t="n">
         <v>99.99186503758035</v>
@@ -1235,7 +1235,7 @@
         <v>0.160559</v>
       </c>
       <c r="C51" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D51" t="n">
         <v>99.99167440383025</v>
@@ -1249,7 +1249,7 @@
         <v>0.163836</v>
       </c>
       <c r="C52" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D52" t="n">
         <v>99.99243629100361</v>
@@ -1263,7 +1263,7 @@
         <v>0.167112</v>
       </c>
       <c r="C53" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D53" t="n">
         <v>99.99249968651651</v>
@@ -1277,7 +1277,7 @@
         <v>0.170389</v>
       </c>
       <c r="C54" t="n">
-        <v>10.04603916208915</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D54" t="n">
         <v>99.99412059202325</v>
@@ -1291,7 +1291,7 @@
         <v>0.173666</v>
       </c>
       <c r="C55" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D55" t="n">
         <v>99.99375980316398</v>
@@ -1305,7 +1305,7 @@
         <v>0.176942</v>
       </c>
       <c r="C56" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D56" t="n">
         <v>99.99223811157054</v>
@@ -1319,7 +1319,7 @@
         <v>0.180219</v>
       </c>
       <c r="C57" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D57" t="n">
         <v>99.99367012878513</v>
@@ -1333,7 +1333,7 @@
         <v>0.183496</v>
       </c>
       <c r="C58" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D58" t="n">
         <v>99.99185367718054</v>
@@ -1347,7 +1347,7 @@
         <v>0.186773</v>
       </c>
       <c r="C59" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D59" t="n">
         <v>99.99562563740081</v>
@@ -1361,7 +1361,7 @@
         <v>0.190049</v>
       </c>
       <c r="C60" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D60" t="n">
         <v>99.99445721193227</v>
@@ -1375,7 +1375,7 @@
         <v>0.193326</v>
       </c>
       <c r="C61" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D61" t="n">
         <v>99.99305882420919</v>
@@ -1389,7 +1389,7 @@
         <v>0.196603</v>
       </c>
       <c r="C62" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D62" t="n">
         <v>99.99241133143684</v>
@@ -1403,7 +1403,7 @@
         <v>0.199879</v>
       </c>
       <c r="C63" t="n">
-        <v>10.04603916208913</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D63" t="n">
         <v>99.9941865660618</v>
@@ -1417,7 +1417,7 @@
         <v>0.203156</v>
       </c>
       <c r="C64" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D64" t="n">
         <v>99.99380735729</v>
@@ -1431,7 +1431,7 @@
         <v>0.206433</v>
       </c>
       <c r="C65" t="n">
-        <v>10.04603916208916</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D65" t="n">
         <v>99.99285703961841</v>
@@ -1445,7 +1445,7 @@
         <v>0.20971</v>
       </c>
       <c r="C66" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D66" t="n">
         <v>99.99415865701967</v>
@@ -1459,7 +1459,7 @@
         <v>0.212986</v>
       </c>
       <c r="C67" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D67" t="n">
         <v>99.99235891944198</v>
@@ -1473,7 +1473,7 @@
         <v>0.216263</v>
       </c>
       <c r="C68" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D68" t="n">
         <v>99.99187741410559</v>
@@ -1487,7 +1487,7 @@
         <v>0.21954</v>
       </c>
       <c r="C69" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D69" t="n">
         <v>99.99283040399393</v>
@@ -1501,7 +1501,7 @@
         <v>0.222816</v>
       </c>
       <c r="C70" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D70" t="n">
         <v>99.99546636718721</v>
@@ -1515,7 +1515,7 @@
         <v>0.226093</v>
       </c>
       <c r="C71" t="n">
-        <v>10.04603916208909</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D71" t="n">
         <v>99.99512622695541</v>
@@ -1529,7 +1529,7 @@
         <v>0.22937</v>
       </c>
       <c r="C72" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D72" t="n">
         <v>99.99612577103149</v>
@@ -1543,7 +1543,7 @@
         <v>0.232647</v>
       </c>
       <c r="C73" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D73" t="n">
         <v>99.99662904101652</v>
@@ -1557,7 +1557,7 @@
         <v>0.235923</v>
       </c>
       <c r="C74" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D74" t="n">
         <v>99.99632719278158</v>
@@ -1571,7 +1571,7 @@
         <v>0.2392</v>
       </c>
       <c r="C75" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D75" t="n">
         <v>99.99919962716555</v>
@@ -1585,7 +1585,7 @@
         <v>0.242477</v>
       </c>
       <c r="C76" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D76" t="n">
         <v>99.99966218258221</v>
@@ -1599,7 +1599,7 @@
         <v>0.245753</v>
       </c>
       <c r="C77" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D77" t="n">
         <v>100.0008625562947</v>
@@ -1613,7 +1613,7 @@
         <v>0.24903</v>
       </c>
       <c r="C78" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D78" t="n">
         <v>100.0022136908329</v>
@@ -1627,7 +1627,7 @@
         <v>0.252307</v>
       </c>
       <c r="C79" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D79" t="n">
         <v>100.0048078924521</v>
@@ -1641,7 +1641,7 @@
         <v>0.255584</v>
       </c>
       <c r="C80" t="n">
-        <v>10.04603916208915</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D80" t="n">
         <v>100.0055764482811</v>
@@ -1655,7 +1655,7 @@
         <v>0.25886</v>
       </c>
       <c r="C81" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D81" t="n">
         <v>100.0075960479311</v>
@@ -1669,7 +1669,7 @@
         <v>0.262137</v>
       </c>
       <c r="C82" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D82" t="n">
         <v>100.0088077744266</v>
@@ -1683,7 +1683,7 @@
         <v>0.265414</v>
       </c>
       <c r="C83" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D83" t="n">
         <v>100.0125048381142</v>
@@ -1697,7 +1697,7 @@
         <v>0.26869</v>
       </c>
       <c r="C84" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D84" t="n">
         <v>100.0159632801173</v>
@@ -1711,7 +1711,7 @@
         <v>0.271967</v>
       </c>
       <c r="C85" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D85" t="n">
         <v>100.0165800575323</v>
@@ -1725,7 +1725,7 @@
         <v>0.275244</v>
       </c>
       <c r="C86" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166615</v>
       </c>
       <c r="D86" t="n">
         <v>100.0204432772347</v>
@@ -1739,7 +1739,7 @@
         <v>0.278521</v>
       </c>
       <c r="C87" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D87" t="n">
         <v>100.0213660956747</v>
@@ -1753,7 +1753,7 @@
         <v>0.281797</v>
       </c>
       <c r="C88" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D88" t="n">
         <v>100.0214627530771</v>
@@ -1767,7 +1767,7 @@
         <v>0.285074</v>
       </c>
       <c r="C89" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D89" t="n">
         <v>100.0198446136076</v>
@@ -1781,7 +1781,7 @@
         <v>0.288351</v>
       </c>
       <c r="C90" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166614</v>
       </c>
       <c r="D90" t="n">
         <v>100.0196806994024</v>
@@ -1795,7 +1795,7 @@
         <v>0.291627</v>
       </c>
       <c r="C91" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D91" t="n">
         <v>100.0175985343327</v>
@@ -1809,7 +1809,7 @@
         <v>0.294904</v>
       </c>
       <c r="C92" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D92" t="n">
         <v>100.0196184090756</v>
@@ -1823,7 +1823,7 @@
         <v>0.298181</v>
       </c>
       <c r="C93" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D93" t="n">
         <v>100.0181083455599</v>
@@ -1837,7 +1837,7 @@
         <v>0.301458</v>
       </c>
       <c r="C94" t="n">
-        <v>10.04603916208909</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D94" t="n">
         <v>100.0188078601302</v>
@@ -1851,7 +1851,7 @@
         <v>0.304734</v>
       </c>
       <c r="C95" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D95" t="n">
         <v>100.0197485747086</v>
@@ -1865,7 +1865,7 @@
         <v>0.308011</v>
       </c>
       <c r="C96" t="n">
-        <v>10.04603916208917</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D96" t="n">
         <v>100.0217869286698</v>
@@ -1879,7 +1879,7 @@
         <v>0.311288</v>
       </c>
       <c r="C97" t="n">
-        <v>10.0460391620891</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D97" t="n">
         <v>100.0235693441021</v>
@@ -1893,7 +1893,7 @@
         <v>0.314564</v>
       </c>
       <c r="C98" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D98" t="n">
         <v>100.0212835489822</v>
@@ -1907,7 +1907,7 @@
         <v>0.317841</v>
       </c>
       <c r="C99" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D99" t="n">
         <v>100.0215632129837</v>
@@ -1921,7 +1921,7 @@
         <v>0.321118</v>
       </c>
       <c r="C100" t="n">
-        <v>10.04603916208917</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D100" t="n">
         <v>100.0213856368848</v>
@@ -1935,7 +1935,7 @@
         <v>0.324395</v>
       </c>
       <c r="C101" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D101" t="n">
         <v>100.020352015458</v>
@@ -1949,7 +1949,7 @@
         <v>0.327671</v>
       </c>
       <c r="C102" t="n">
-        <v>10.04603916208918</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D102" t="n">
         <v>100.0219554182161</v>
@@ -1963,7 +1963,7 @@
         <v>0.330948</v>
       </c>
       <c r="C103" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D103" t="n">
         <v>100.0225387020617</v>
@@ -1977,7 +1977,7 @@
         <v>0.334225</v>
       </c>
       <c r="C104" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D104" t="n">
         <v>100.023435386116</v>
@@ -1991,7 +1991,7 @@
         <v>0.337501</v>
       </c>
       <c r="C105" t="n">
-        <v>10.04603916208913</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D105" t="n">
         <v>100.0204741289531</v>
@@ -2005,7 +2005,7 @@
         <v>0.340778</v>
       </c>
       <c r="C106" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D106" t="n">
         <v>100.0183172242062</v>
@@ -2019,7 +2019,7 @@
         <v>0.344055</v>
       </c>
       <c r="C107" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D107" t="n">
         <v>100.0205384808732</v>
@@ -2033,7 +2033,7 @@
         <v>0.347332</v>
       </c>
       <c r="C108" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D108" t="n">
         <v>100.0207228998879</v>
@@ -2047,7 +2047,7 @@
         <v>0.350608</v>
       </c>
       <c r="C109" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D109" t="n">
         <v>100.0204188215809</v>
@@ -2061,7 +2061,7 @@
         <v>0.353885</v>
       </c>
       <c r="C110" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166604</v>
       </c>
       <c r="D110" t="n">
         <v>100.022087899083</v>
@@ -2075,7 +2075,7 @@
         <v>0.357162</v>
       </c>
       <c r="C111" t="n">
-        <v>10.04603916208909</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D111" t="n">
         <v>100.0233605993515</v>
@@ -2089,7 +2089,7 @@
         <v>0.360438</v>
       </c>
       <c r="C112" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D112" t="n">
         <v>100.0202823881721</v>
@@ -2103,7 +2103,7 @@
         <v>0.363715</v>
       </c>
       <c r="C113" t="n">
-        <v>10.04603916208907</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D113" t="n">
         <v>100.0210039226547</v>
@@ -2117,7 +2117,7 @@
         <v>0.366992</v>
       </c>
       <c r="C114" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D114" t="n">
         <v>100.0190848157457</v>
@@ -2131,7 +2131,7 @@
         <v>0.370268</v>
       </c>
       <c r="C115" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D115" t="n">
         <v>100.0197695317335</v>
@@ -2145,7 +2145,7 @@
         <v>0.373545</v>
       </c>
       <c r="C116" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D116" t="n">
         <v>100.0220460155908</v>
@@ -2159,7 +2159,7 @@
         <v>0.376822</v>
       </c>
       <c r="C117" t="n">
-        <v>10.04603916208911</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D117" t="n">
         <v>100.0246820543794</v>
@@ -2173,7 +2173,7 @@
         <v>0.380099</v>
       </c>
       <c r="C118" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D118" t="n">
         <v>100.0253701534251</v>
@@ -2187,7 +2187,7 @@
         <v>0.383375</v>
       </c>
       <c r="C119" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D119" t="n">
         <v>100.0232000284083</v>
@@ -2201,7 +2201,7 @@
         <v>0.386652</v>
       </c>
       <c r="C120" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D120" t="n">
         <v>100.0288868299229</v>
@@ -2215,7 +2215,7 @@
         <v>0.389929</v>
       </c>
       <c r="C121" t="n">
-        <v>10.04603916208914</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D121" t="n">
         <v>100.0279760535154</v>
@@ -2229,7 +2229,7 @@
         <v>0.393205</v>
       </c>
       <c r="C122" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D122" t="n">
         <v>100.0291852453017</v>
@@ -2243,7 +2243,7 @@
         <v>0.396482</v>
       </c>
       <c r="C123" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D123" t="n">
         <v>100.029205107279</v>
@@ -2257,7 +2257,7 @@
         <v>0.399759</v>
       </c>
       <c r="C124" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D124" t="n">
         <v>100.03323015856</v>
@@ -2271,7 +2271,7 @@
         <v>0.403036</v>
       </c>
       <c r="C125" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D125" t="n">
         <v>100.0344948160492</v>
@@ -2285,7 +2285,7 @@
         <v>0.406312</v>
       </c>
       <c r="C126" t="n">
-        <v>10.04603916208914</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D126" t="n">
         <v>100.0364402075072</v>
@@ -2299,7 +2299,7 @@
         <v>0.409589</v>
       </c>
       <c r="C127" t="n">
-        <v>10.04603916208908</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D127" t="n">
         <v>100.040037970139</v>
@@ -2313,7 +2313,7 @@
         <v>0.412866</v>
       </c>
       <c r="C128" t="n">
-        <v>10.04603916208911</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D128" t="n">
         <v>100.0413387291998</v>
@@ -2327,7 +2327,7 @@
         <v>0.416142</v>
       </c>
       <c r="C129" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D129" t="n">
         <v>100.0400687203349</v>
@@ -2341,7 +2341,7 @@
         <v>0.419419</v>
       </c>
       <c r="C130" t="n">
-        <v>10.04603916208916</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D130" t="n">
         <v>100.0386984847119</v>
@@ -2355,7 +2355,7 @@
         <v>0.422696</v>
       </c>
       <c r="C131" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D131" t="n">
         <v>100.0412177866076</v>
@@ -2369,7 +2369,7 @@
         <v>0.425973</v>
       </c>
       <c r="C132" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D132" t="n">
         <v>100.0383681638215</v>
@@ -2383,7 +2383,7 @@
         <v>0.429249</v>
       </c>
       <c r="C133" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D133" t="n">
         <v>100.0442421727293</v>
@@ -2397,7 +2397,7 @@
         <v>0.432526</v>
       </c>
       <c r="C134" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D134" t="n">
         <v>100.0432146074117</v>
@@ -2411,7 +2411,7 @@
         <v>0.435803</v>
       </c>
       <c r="C135" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D135" t="n">
         <v>100.0407239710936</v>
@@ -2425,7 +2425,7 @@
         <v>0.439079</v>
       </c>
       <c r="C136" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D136" t="n">
         <v>100.036907923672</v>
@@ -2439,7 +2439,7 @@
         <v>0.442356</v>
       </c>
       <c r="C137" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D137" t="n">
         <v>100.03904490521</v>
@@ -2453,7 +2453,7 @@
         <v>0.445633</v>
       </c>
       <c r="C138" t="n">
-        <v>10.04603916208916</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D138" t="n">
         <v>100.0400238326964</v>
@@ -2467,7 +2467,7 @@
         <v>0.44891</v>
       </c>
       <c r="C139" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D139" t="n">
         <v>100.0405803285944</v>
@@ -2481,7 +2481,7 @@
         <v>0.452186</v>
       </c>
       <c r="C140" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D140" t="n">
         <v>100.03720708671</v>
@@ -2495,7 +2495,7 @@
         <v>0.455463</v>
       </c>
       <c r="C141" t="n">
-        <v>10.04603916208912</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D141" t="n">
         <v>100.0386733521395</v>
@@ -2509,7 +2509,7 @@
         <v>0.45874</v>
       </c>
       <c r="C142" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D142" t="n">
         <v>100.0371188869923</v>
@@ -2523,7 +2523,7 @@
         <v>0.462016</v>
       </c>
       <c r="C143" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D143" t="n">
         <v>100.0372425966174</v>
@@ -2537,7 +2537,7 @@
         <v>0.465293</v>
       </c>
       <c r="C144" t="n">
-        <v>10.04603916208913</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D144" t="n">
         <v>100.035918741152</v>
@@ -2551,7 +2551,7 @@
         <v>0.46857</v>
       </c>
       <c r="C145" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D145" t="n">
         <v>100.0313878345802</v>
@@ -2565,7 +2565,7 @@
         <v>0.471847</v>
       </c>
       <c r="C146" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166604</v>
       </c>
       <c r="D146" t="n">
         <v>100.0285410688765</v>
@@ -2579,7 +2579,7 @@
         <v>0.475123</v>
       </c>
       <c r="C147" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D147" t="n">
         <v>100.0310426116721</v>
@@ -2593,7 +2593,7 @@
         <v>0.4784</v>
       </c>
       <c r="C148" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D148" t="n">
         <v>100.0296476942821</v>
@@ -2607,7 +2607,7 @@
         <v>0.481677</v>
       </c>
       <c r="C149" t="n">
-        <v>10.04603916208916</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D149" t="n">
         <v>100.0283713521238</v>
@@ -2621,7 +2621,7 @@
         <v>0.484953</v>
       </c>
       <c r="C150" t="n">
-        <v>10.04603916208914</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D150" t="n">
         <v>100.031114005511</v>
@@ -2635,7 +2635,7 @@
         <v>0.48823</v>
       </c>
       <c r="C151" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D151" t="n">
         <v>100.0315292383722</v>
@@ -2649,7 +2649,7 @@
         <v>0.491507</v>
       </c>
       <c r="C152" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D152" t="n">
         <v>100.0285091033781</v>
@@ -2663,7 +2663,7 @@
         <v>0.494784</v>
       </c>
       <c r="C153" t="n">
-        <v>10.04603916208909</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D153" t="n">
         <v>100.0299867662424</v>
@@ -2677,7 +2677,7 @@
         <v>0.49806</v>
       </c>
       <c r="C154" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D154" t="n">
         <v>100.0325619715356</v>
@@ -2691,7 +2691,7 @@
         <v>0.501337</v>
       </c>
       <c r="C155" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D155" t="n">
         <v>100.0360294599849</v>
@@ -2705,7 +2705,7 @@
         <v>0.504614</v>
       </c>
       <c r="C156" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D156" t="n">
         <v>100.0415514373418</v>
@@ -2719,7 +2719,7 @@
         <v>0.50789</v>
       </c>
       <c r="C157" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D157" t="n">
         <v>100.0422117459062</v>
@@ -2733,7 +2733,7 @@
         <v>0.511167</v>
       </c>
       <c r="C158" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D158" t="n">
         <v>100.0399878832083</v>
@@ -2747,7 +2747,7 @@
         <v>0.514444</v>
       </c>
       <c r="C159" t="n">
-        <v>10.04603916208914</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D159" t="n">
         <v>100.0368246351395</v>
@@ -2761,7 +2761,7 @@
         <v>0.517721</v>
       </c>
       <c r="C160" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166613</v>
       </c>
       <c r="D160" t="n">
         <v>100.034208613999</v>
@@ -2775,7 +2775,7 @@
         <v>0.520997</v>
       </c>
       <c r="C161" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D161" t="n">
         <v>100.0291222303817</v>
@@ -2789,7 +2789,7 @@
         <v>0.524274</v>
       </c>
       <c r="C162" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D162" t="n">
         <v>100.0276493702248</v>
@@ -2803,7 +2803,7 @@
         <v>0.527551</v>
       </c>
       <c r="C163" t="n">
-        <v>10.04603916208907</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D163" t="n">
         <v>100.0241886219908</v>
@@ -2817,7 +2817,7 @@
         <v>0.530827</v>
       </c>
       <c r="C164" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D164" t="n">
         <v>100.0260289262958</v>
@@ -2831,7 +2831,7 @@
         <v>0.534104</v>
       </c>
       <c r="C165" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D165" t="n">
         <v>100.0248595085448</v>
@@ -2845,7 +2845,7 @@
         <v>0.537381</v>
       </c>
       <c r="C166" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D166" t="n">
         <v>100.0274361642422</v>
@@ -2859,7 +2859,7 @@
         <v>0.540658</v>
       </c>
       <c r="C167" t="n">
-        <v>10.04603916208914</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D167" t="n">
         <v>100.0241853030324</v>
@@ -2873,7 +2873,7 @@
         <v>0.543934</v>
       </c>
       <c r="C168" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D168" t="n">
         <v>100.0245871172751</v>
@@ -2887,7 +2887,7 @@
         <v>0.547211</v>
       </c>
       <c r="C169" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D169" t="n">
         <v>100.0293942554767</v>
@@ -2901,7 +2901,7 @@
         <v>0.550488</v>
       </c>
       <c r="C170" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D170" t="n">
         <v>100.0285971033411</v>
@@ -2915,7 +2915,7 @@
         <v>0.553764</v>
       </c>
       <c r="C171" t="n">
-        <v>10.04603916208913</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D171" t="n">
         <v>100.0308592322743</v>
@@ -2929,7 +2929,7 @@
         <v>0.557041</v>
       </c>
       <c r="C172" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D172" t="n">
         <v>100.0302669023232</v>
@@ -2943,7 +2943,7 @@
         <v>0.560318</v>
       </c>
       <c r="C173" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D173" t="n">
         <v>100.0265524710339</v>
@@ -2957,7 +2957,7 @@
         <v>0.563595</v>
       </c>
       <c r="C174" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D174" t="n">
         <v>100.0283776189602</v>
@@ -2971,7 +2971,7 @@
         <v>0.566871</v>
       </c>
       <c r="C175" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D175" t="n">
         <v>100.0260560109022</v>
@@ -2985,7 +2985,7 @@
         <v>0.570148</v>
       </c>
       <c r="C176" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D176" t="n">
         <v>100.0276311720824</v>
@@ -2999,7 +2999,7 @@
         <v>0.573425</v>
       </c>
       <c r="C177" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D177" t="n">
         <v>100.0277509393717</v>
@@ -3013,7 +3013,7 @@
         <v>0.576701</v>
       </c>
       <c r="C178" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D178" t="n">
         <v>100.0316338893899</v>
@@ -3027,7 +3027,7 @@
         <v>0.579978</v>
       </c>
       <c r="C179" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166603</v>
       </c>
       <c r="D179" t="n">
         <v>100.0278716827952</v>
@@ -3041,7 +3041,7 @@
         <v>0.583255</v>
       </c>
       <c r="C180" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D180" t="n">
         <v>100.0284102119051</v>
@@ -3055,7 +3055,7 @@
         <v>0.5865320000000001</v>
       </c>
       <c r="C181" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D181" t="n">
         <v>100.0275669679974</v>
@@ -3069,7 +3069,7 @@
         <v>0.589808</v>
       </c>
       <c r="C182" t="n">
-        <v>10.04603916208913</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D182" t="n">
         <v>100.031046251674</v>
@@ -3083,7 +3083,7 @@
         <v>0.593085</v>
       </c>
       <c r="C183" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D183" t="n">
         <v>100.0316707465932</v>
@@ -3097,7 +3097,7 @@
         <v>0.5963619999999999</v>
       </c>
       <c r="C184" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D184" t="n">
         <v>100.0288838454437</v>
@@ -3111,7 +3111,7 @@
         <v>0.599638</v>
       </c>
       <c r="C185" t="n">
-        <v>10.04603916208909</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D185" t="n">
         <v>100.0293174730849</v>
@@ -3125,7 +3125,7 @@
         <v>0.602915</v>
       </c>
       <c r="C186" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D186" t="n">
         <v>100.0282147372145</v>
@@ -3139,7 +3139,7 @@
         <v>0.606192</v>
       </c>
       <c r="C187" t="n">
-        <v>10.04603916208914</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D187" t="n">
         <v>100.0272404736733</v>
@@ -3153,7 +3153,7 @@
         <v>0.609468</v>
       </c>
       <c r="C188" t="n">
-        <v>10.04603916208909</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D188" t="n">
         <v>100.0275806802611</v>
@@ -3167,7 +3167,7 @@
         <v>0.612745</v>
       </c>
       <c r="C189" t="n">
-        <v>10.04603916208915</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D189" t="n">
         <v>100.0300017778193</v>
@@ -3181,7 +3181,7 @@
         <v>0.616022</v>
       </c>
       <c r="C190" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D190" t="n">
         <v>100.0309246624531</v>
@@ -3195,7 +3195,7 @@
         <v>0.619299</v>
       </c>
       <c r="C191" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D191" t="n">
         <v>100.0308730220013</v>
@@ -3209,7 +3209,7 @@
         <v>0.622575</v>
       </c>
       <c r="C192" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D192" t="n">
         <v>100.0298107034886</v>
@@ -3223,7 +3223,7 @@
         <v>0.625852</v>
       </c>
       <c r="C193" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D193" t="n">
         <v>100.031110704211</v>
@@ -3237,7 +3237,7 @@
         <v>0.629129</v>
       </c>
       <c r="C194" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D194" t="n">
         <v>100.0320624860898</v>
@@ -3251,7 +3251,7 @@
         <v>0.632405</v>
       </c>
       <c r="C195" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D195" t="n">
         <v>100.03508377573</v>
@@ -3265,7 +3265,7 @@
         <v>0.635682</v>
       </c>
       <c r="C196" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D196" t="n">
         <v>100.0369385496355</v>
@@ -3279,7 +3279,7 @@
         <v>0.6389590000000001</v>
       </c>
       <c r="C197" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D197" t="n">
         <v>100.0384818708962</v>
@@ -3293,7 +3293,7 @@
         <v>0.642236</v>
       </c>
       <c r="C198" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D198" t="n">
         <v>100.0378038438172</v>
@@ -3307,7 +3307,7 @@
         <v>0.645512</v>
       </c>
       <c r="C199" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D199" t="n">
         <v>100.0436382307504</v>
@@ -3321,7 +3321,7 @@
         <v>0.6487889999999999</v>
       </c>
       <c r="C200" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D200" t="n">
         <v>100.0439000582965</v>
@@ -3335,7 +3335,7 @@
         <v>0.652066</v>
       </c>
       <c r="C201" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D201" t="n">
         <v>100.0371503486638</v>
@@ -3349,7 +3349,7 @@
         <v>0.655342</v>
       </c>
       <c r="C202" t="n">
-        <v>10.0460391620891</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D202" t="n">
         <v>100.0316088887487</v>
@@ -3363,7 +3363,7 @@
         <v>0.658619</v>
       </c>
       <c r="C203" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D203" t="n">
         <v>100.0328703861844</v>
@@ -3377,7 +3377,7 @@
         <v>0.661896</v>
       </c>
       <c r="C204" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D204" t="n">
         <v>100.034913905176</v>
@@ -3391,7 +3391,7 @@
         <v>0.665173</v>
       </c>
       <c r="C205" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D205" t="n">
         <v>100.0379786388776</v>
@@ -3405,7 +3405,7 @@
         <v>0.668449</v>
       </c>
       <c r="C206" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D206" t="n">
         <v>100.0379546592469</v>
@@ -3419,7 +3419,7 @@
         <v>0.671726</v>
       </c>
       <c r="C207" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D207" t="n">
         <v>100.0337919802352</v>
@@ -3433,7 +3433,7 @@
         <v>0.675003</v>
       </c>
       <c r="C208" t="n">
-        <v>10.04603916208913</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D208" t="n">
         <v>100.0327966501418</v>
@@ -3447,7 +3447,7 @@
         <v>0.678279</v>
       </c>
       <c r="C209" t="n">
-        <v>10.04603916208912</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D209" t="n">
         <v>100.0262318817591</v>
@@ -3461,7 +3461,7 @@
         <v>0.6815560000000001</v>
       </c>
       <c r="C210" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D210" t="n">
         <v>100.0246080362995</v>
@@ -3475,7 +3475,7 @@
         <v>0.684833</v>
       </c>
       <c r="C211" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166606</v>
       </c>
       <c r="D211" t="n">
         <v>100.022531244311</v>
@@ -3489,7 +3489,7 @@
         <v>0.68811</v>
       </c>
       <c r="C212" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D212" t="n">
         <v>100.0234502161989</v>
@@ -3503,7 +3503,7 @@
         <v>0.6913859999999999</v>
       </c>
       <c r="C213" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D213" t="n">
         <v>100.0200493165806</v>
@@ -3517,7 +3517,7 @@
         <v>0.694663</v>
       </c>
       <c r="C214" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D214" t="n">
         <v>100.0272903198385</v>
@@ -3531,7 +3531,7 @@
         <v>0.69794</v>
       </c>
       <c r="C215" t="n">
-        <v>10.04603916208912</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D215" t="n">
         <v>100.0307477681974</v>
@@ -3545,7 +3545,7 @@
         <v>0.701216</v>
       </c>
       <c r="C216" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D216" t="n">
         <v>100.0286117245682</v>
@@ -3559,7 +3559,7 @@
         <v>0.704493</v>
       </c>
       <c r="C217" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D217" t="n">
         <v>100.0278527119615</v>
@@ -3573,7 +3573,7 @@
         <v>0.70777</v>
       </c>
       <c r="C218" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D218" t="n">
         <v>100.0310208763219</v>
@@ -3587,7 +3587,7 @@
         <v>0.711047</v>
       </c>
       <c r="C219" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D219" t="n">
         <v>100.0273069358324</v>
@@ -3601,7 +3601,7 @@
         <v>0.714323</v>
       </c>
       <c r="C220" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166609</v>
       </c>
       <c r="D220" t="n">
         <v>100.030345310313</v>
@@ -3615,7 +3615,7 @@
         <v>0.7176</v>
       </c>
       <c r="C221" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166611</v>
       </c>
       <c r="D221" t="n">
         <v>100.0298404285571</v>
@@ -3629,7 +3629,7 @@
         <v>0.720877</v>
       </c>
       <c r="C222" t="n">
-        <v>10.04603916208909</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D222" t="n">
         <v>100.0323918649384</v>
@@ -3643,7 +3643,7 @@
         <v>0.724153</v>
       </c>
       <c r="C223" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166605</v>
       </c>
       <c r="D223" t="n">
         <v>100.0336325572049</v>
@@ -3657,7 +3657,7 @@
         <v>0.72743</v>
       </c>
       <c r="C224" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D224" t="n">
         <v>100.0307681744935</v>
@@ -3671,7 +3671,7 @@
         <v>0.730707</v>
       </c>
       <c r="C225" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166607</v>
       </c>
       <c r="D225" t="n">
         <v>100.0286376021413</v>
@@ -3685,7 +3685,7 @@
         <v>0.733984</v>
       </c>
       <c r="C226" t="n">
-        <v>10.04603916208913</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D226" t="n">
         <v>100.0337230276616</v>
@@ -3699,7 +3699,7 @@
         <v>0.73726</v>
       </c>
       <c r="C227" t="n">
-        <v>10.04603916208914</v>
+        <v>11.05161757166612</v>
       </c>
       <c r="D227" t="n">
         <v>100.0301105289928</v>
@@ -3713,7 +3713,7 @@
         <v>0.740537</v>
       </c>
       <c r="C228" t="n">
-        <v>10.04603916208915</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D228" t="n">
         <v>100.030847901226</v>
@@ -3727,7 +3727,7 @@
         <v>0.743814</v>
       </c>
       <c r="C229" t="n">
-        <v>10.04603916208915</v>
+        <v>11.05161757166604</v>
       </c>
       <c r="D229" t="n">
         <v>100.0345684487924</v>
@@ -3741,7 +3741,7 @@
         <v>0.74709</v>
       </c>
       <c r="C230" t="n">
-        <v>10.04603916208915</v>
+        <v>11.0516175716661</v>
       </c>
       <c r="D230" t="n">
         <v>100.0386723067022</v>
@@ -3755,7 +3755,7 @@
         <v>0.750367</v>
       </c>
       <c r="C231" t="n">
-        <v>10.04603916208911</v>
+        <v>11.05161757166608</v>
       </c>
       <c r="D231" t="n">
         <v>100.0429794596231</v>
@@ -3769,7 +3769,7 @@
         <v>0.753644</v>
       </c>
       <c r="C232" t="n">
-        <v>10.04603916208912</v>
+        <v>10.04895838390469</v>
       </c>
       <c r="D232" t="n">
         <v>97.26845424561363</v>
@@ -3783,7 +3783,7 @@
         <v>0.756921</v>
       </c>
       <c r="C233" t="n">
-        <v>10.04603916208913</v>
+        <v>10.0489583839047</v>
       </c>
       <c r="D233" t="n">
         <v>97.26991386758291</v>
@@ -3797,7 +3797,7 @@
         <v>0.760197</v>
       </c>
       <c r="C234" t="n">
-        <v>10.04603916208912</v>
+        <v>10.04895838390469</v>
       </c>
       <c r="D234" t="n">
         <v>97.27116483637452</v>
@@ -3811,7 +3811,7 @@
         <v>0.763474</v>
       </c>
       <c r="C235" t="n">
-        <v>10.04603916208912</v>
+        <v>10.04895838390469</v>
       </c>
       <c r="D235" t="n">
         <v>97.27167888503169</v>
@@ -3825,7 +3825,7 @@
         <v>0.766751</v>
       </c>
       <c r="C236" t="n">
-        <v>10.04603916208914</v>
+        <v>10.04895838390471</v>
       </c>
       <c r="D236" t="n">
         <v>97.27605432578216</v>
@@ -3839,7 +3839,7 @@
         <v>0.770027</v>
       </c>
       <c r="C237" t="n">
-        <v>10.04603916208912</v>
+        <v>10.04895838390469</v>
       </c>
       <c r="D237" t="n">
         <v>97.27791855119774</v>
@@ -3853,7 +3853,7 @@
         <v>0.773304</v>
       </c>
       <c r="C238" t="n">
-        <v>10.0460391620891</v>
+        <v>10.04895838390467</v>
       </c>
       <c r="D238" t="n">
         <v>97.27771007231379</v>
@@ -3867,7 +3867,7 @@
         <v>0.776581</v>
       </c>
       <c r="C239" t="n">
-        <v>10.04603916208909</v>
+        <v>10.04895838390466</v>
       </c>
       <c r="D239" t="n">
         <v>97.27963946746934</v>
@@ -3881,7 +3881,7 @@
         <v>0.7798580000000001</v>
       </c>
       <c r="C240" t="n">
-        <v>10.04603916208912</v>
+        <v>10.04895838390468</v>
       </c>
       <c r="D240" t="n">
         <v>97.27771733270754</v>
@@ -3895,7 +3895,7 @@
         <v>0.783134</v>
       </c>
       <c r="C241" t="n">
-        <v>10.04603916208911</v>
+        <v>10.04895838390468</v>
       </c>
       <c r="D241" t="n">
         <v>97.28270696719278</v>
@@ -3909,7 +3909,7 @@
         <v>0.786411</v>
       </c>
       <c r="C242" t="n">
-        <v>10.04603916208912</v>
+        <v>10.0494314940003</v>
       </c>
       <c r="D242" t="n">
         <v>97.28060839669583</v>
@@ -3923,7 +3923,7 @@
         <v>0.7896879999999999</v>
       </c>
       <c r="C243" t="n">
-        <v>10.04603916208913</v>
+        <v>10.04757703479683</v>
       </c>
       <c r="D243" t="n">
         <v>97.27923609067345</v>
@@ -3937,7 +3937,7 @@
         <v>0.792964</v>
       </c>
       <c r="C244" t="n">
-        <v>10.04603916208916</v>
+        <v>10.04757703479686</v>
       </c>
       <c r="D244" t="n">
         <v>97.27666734782373</v>
@@ -3951,7 +3951,7 @@
         <v>0.796241</v>
       </c>
       <c r="C245" t="n">
-        <v>10.04603916208914</v>
+        <v>10.04757703479684</v>
       </c>
       <c r="D245" t="n">
         <v>97.27455013846539</v>
@@ -3965,7 +3965,7 @@
         <v>0.799518</v>
       </c>
       <c r="C246" t="n">
-        <v>10.04603916208908</v>
+        <v>10.04757703479678</v>
       </c>
       <c r="D246" t="n">
         <v>97.27222123711313</v>
@@ -3979,7 +3979,7 @@
         <v>0.802795</v>
       </c>
       <c r="C247" t="n">
-        <v>10.04603916208912</v>
+        <v>10.04757703479682</v>
       </c>
       <c r="D247" t="n">
         <v>97.27384338997338</v>
@@ -3993,7 +3993,7 @@
         <v>0.806071</v>
       </c>
       <c r="C248" t="n">
-        <v>10.04603916208916</v>
+        <v>10.04757703479686</v>
       </c>
       <c r="D248" t="n">
         <v>97.27455733163279</v>
@@ -4007,7 +4007,7 @@
         <v>0.809348</v>
       </c>
       <c r="C249" t="n">
-        <v>10.04603916208912</v>
+        <v>10.04757703479682</v>
       </c>
       <c r="D249" t="n">
         <v>97.2753859595002</v>
@@ -4021,7 +4021,7 @@
         <v>0.812625</v>
       </c>
       <c r="C250" t="n">
-        <v>10.04603916208911</v>
+        <v>10.04761595251394</v>
       </c>
       <c r="D250" t="n">
         <v>97.27724428923958</v>
@@ -4035,7 +4035,7 @@
         <v>0.815901</v>
       </c>
       <c r="C251" t="n">
-        <v>10.04603916208914</v>
+        <v>10.04751636460968</v>
       </c>
       <c r="D251" t="n">
         <v>97.27686906991498</v>
